--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486766_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486766_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6566</v>
+        <v>3.2014</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9629</v>
+        <v>5.3835</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3063</v>
+        <v>-2.1821</v>
       </c>
       <c r="G2" t="n">
         <v>0.2207</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5721</v>
+        <v>-1.0273</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6898</v>
+        <v>-0.2692</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8823</v>
+        <v>-0.7581</v>
       </c>
       <c r="V2" t="n">
         <v>1.8842</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ABITBOL VIERA</t>
+          <t>K. RODRIGUEZ AGUILERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9136</v>
+        <v>1.4823</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4479</v>
+        <v>3.638</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5342</v>
+        <v>-2.1557</v>
       </c>
       <c r="G3" t="n">
-        <v>0.827</v>
+        <v>-0.1721</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2693</v>
+        <v>2.3938</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4423</v>
+        <v>-2.5659</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3102</v>
+        <v>3.3257</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2695</v>
+        <v>1.9806</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>1.3451</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4832</v>
+        <v>-3.4978</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0002</v>
+        <v>0.4132</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.483</v>
+        <v>-3.911</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9654</v>
+        <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0866</v>
+        <v>-0.793</v>
       </c>
       <c r="T3" t="n">
-        <v>1.103</v>
+        <v>-0.1038</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0164</v>
+        <v>-0.6892</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.0266</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.3122</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>M. ABITBOL VIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4989</v>
+        <v>1.1648</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2145</v>
+        <v>1.7239</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7156</v>
+        <v>-0.5591</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3318</v>
+        <v>0.827</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7255</v>
+        <v>2.2693</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0573</v>
+        <v>-1.4423</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1868</v>
+        <v>2.3102</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1054</v>
+        <v>2.2695</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5186</v>
+        <v>-1.4832</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3799</v>
+        <v>-0.0002</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1387</v>
+        <v>-1.483</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2039</v>
+        <v>0.3378</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1107</v>
+        <v>0.3791</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0413</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0692</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. RODRIGUEZ AGUILERA</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3997</v>
+        <v>1.0548</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8037</v>
+        <v>4.118</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.404</v>
+        <v>-3.0632</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1721</v>
+        <v>-0.3318</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3938</v>
+        <v>1.7255</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5659</v>
+        <v>-2.0573</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3257</v>
+        <v>3.1868</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9806</v>
+        <v>3.1054</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3451</v>
+        <v>0.0814</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.4978</v>
+        <v>-3.5186</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4132</v>
+        <v>-1.3799</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.911</v>
+        <v>-2.1387</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3169</v>
+        <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8756</v>
+        <v>-0.648</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9381</v>
+        <v>-0.2072</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9375</v>
+        <v>-0.4408</v>
       </c>
       <c r="V5" t="n">
-        <v>3.0266</v>
+        <v>1.8415</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3122</v>
+        <v>3.0692</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8231</v>
+        <v>-1.2563</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9464</v>
+        <v>-0.4292</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8767</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9817</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2356</v>
+        <v>-0.6688</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7174</v>
+        <v>-0.2003</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5182</v>
+        <v>-0.4686</v>
       </c>
       <c r="V6" t="n">
         <v>0.0426</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CRUJEIRAS MOREIRAS</t>
+          <t>A. ALONSO LANTIGUA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.974</v>
+        <v>-3.0346</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9486</v>
+        <v>-2.4284</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0253</v>
+        <v>-0.6062</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.487</v>
+        <v>-4.3394</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0619</v>
+        <v>-1.3237</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.425</v>
+        <v>-3.0157</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-2.7178</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7168</v>
+        <v>-0.7715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6511</v>
+        <v>-1.9464</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4212</v>
+        <v>-1.6215</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3451</v>
+        <v>-0.5522</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0761</v>
+        <v>-1.0693</v>
       </c>
       <c r="P7" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.9654</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2593</v>
+        <v>-1.124</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0825</v>
+        <v>-0.3244</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3418</v>
+        <v>-0.7996</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2277</v>
+        <v>1.2703</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>M. CRUJEIRAS MOREIRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4176</v>
+        <v>-3.1767</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1073</v>
+        <v>-1.0521</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3103</v>
+        <v>-2.1246</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8282</v>
+        <v>-1.487</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8961</v>
+        <v>-1.0619</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9321</v>
+        <v>-0.425</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5098</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.139</v>
+        <v>-0.7168</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6488</v>
+        <v>0.6511</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3184</v>
+        <v>-1.4212</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0351</v>
+        <v>-0.3451</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2833</v>
+        <v>-1.0761</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1749</v>
+        <v>-0.462</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4338</v>
+        <v>-0.0209</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2589</v>
+        <v>-0.4411</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4707</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALONSO LANTIGUA</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4442</v>
+        <v>-4.0064</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7386</v>
+        <v>-0.7209</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7055</v>
+        <v>-3.2854</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.3394</v>
+        <v>-3.8282</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3237</v>
+        <v>-0.8961</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0157</v>
+        <v>-2.9321</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7178</v>
+        <v>-0.5098</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7715</v>
+        <v>0.139</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9464</v>
+        <v>-0.6488</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6215</v>
+        <v>-3.3184</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5522</v>
+        <v>-1.0351</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0693</v>
+        <v>-2.2833</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1585</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1585</v>
+        <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5336</v>
+        <v>0.5861</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6347</v>
+        <v>0.8202</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8989</v>
+        <v>-0.234</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2703</v>
+        <v>-0.5712</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6138</v>
+        <v>0.8995</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6565</v>
+        <v>-1.4707</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4079</v>
+        <v>-5.4755</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7839</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.1918</v>
+        <v>-6.2663</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6655</v>
@@ -1234,13 +1234,13 @@
         <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5461</v>
+        <v>-0.6136</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2211</v>
+        <v>-0.2141</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.325</v>
+        <v>-0.3995</v>
       </c>
       <c r="V10" t="n">
         <v>-3.9687</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.598</v>
+        <v>-10.0462</v>
       </c>
       <c r="E11" t="n">
-        <v>10.472</v>
+        <v>11.0236</v>
       </c>
       <c r="F11" t="n">
         <v>-21.0697</v>
@@ -1297,7 +1297,7 @@
         <v>-22.9403</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.1424</v>
+        <v>-4.142399999999999</v>
       </c>
       <c r="O11" t="n">
         <v>-18.7979</v>
@@ -1312,16 +1312,16 @@
         <v>14.4809</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.9647</v>
+        <v>-4.412800000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6925</v>
+        <v>-0.1406000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>-4.2722</v>
       </c>
       <c r="V11" t="n">
-        <v>2.2976</v>
+        <v>2.297599999999999</v>
       </c>
       <c r="W11" t="n">
         <v>10.6357</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.5935</v>
+        <v>5.6569</v>
       </c>
       <c r="E12" t="n">
         <v>5.2442</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3492</v>
+        <v>0.4126</v>
       </c>
       <c r="G12" t="n">
         <v>5.69</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8882</v>
+        <v>0.9516</v>
       </c>
       <c r="T12" t="n">
         <v>0.5512</v>
       </c>
       <c r="U12" t="n">
-        <v>0.337</v>
+        <v>0.4004</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9847</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9831</v>
+        <v>3.8396</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6397</v>
+        <v>5.4328</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6566</v>
+        <v>-1.5932</v>
       </c>
       <c r="G13" t="n">
         <v>5.0934</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3571</v>
+        <v>1.2136</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7443</v>
+        <v>0.5375</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6128</v>
+        <v>0.6762</v>
       </c>
       <c r="V13" t="n">
         <v>0.0426</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1202</v>
+        <v>2.8922</v>
       </c>
       <c r="E14" t="n">
-        <v>5.164</v>
+        <v>3.5551</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0438</v>
+        <v>-0.6629</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9822</v>
+        <v>2.3279</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7449</v>
+        <v>0.2684</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2373</v>
+        <v>2.0595</v>
       </c>
       <c r="J14" t="n">
-        <v>6.1006</v>
+        <v>2.6046</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8836</v>
+        <v>1.0967</v>
       </c>
       <c r="L14" t="n">
-        <v>3.217</v>
+        <v>1.5079</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1184</v>
+        <v>-0.2767</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1387</v>
+        <v>-0.8283</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0203</v>
+        <v>0.5516</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7031</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2119</v>
+        <v>0.1862</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0681</v>
+        <v>0.117</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1438</v>
+        <v>0.0692</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3709</v>
+        <v>0.5712</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8568</v>
+        <v>1.7989</v>
       </c>
       <c r="X14" t="n">
         <v>-1.2277</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6746</v>
+        <v>2.6387</v>
       </c>
       <c r="E15" t="n">
         <v>2.5225</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1522</v>
+        <v>0.1162</v>
       </c>
       <c r="G15" t="n">
         <v>-1.8299</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9253</v>
+        <v>1.8893</v>
       </c>
       <c r="T15" t="n">
         <v>1.0202</v>
       </c>
       <c r="U15" t="n">
-        <v>0.905</v>
+        <v>0.8691</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4178</v>
+        <v>1.9752</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3273</v>
+        <v>1.8102</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0905</v>
+        <v>0.165</v>
       </c>
       <c r="G16" t="n">
         <v>0.1378</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1528</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.103</v>
+        <v>0.5859</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0498</v>
+        <v>0.1243</v>
       </c>
       <c r="V16" t="n">
         <v>1.5133</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0551</v>
+        <v>1.7839</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8311</v>
+        <v>4.0263</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.776</v>
+        <v>-2.2425</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3279</v>
+        <v>3.9822</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2684</v>
+        <v>0.7449</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0595</v>
+        <v>3.2373</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6046</v>
+        <v>6.1006</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0967</v>
+        <v>2.8836</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5079</v>
+        <v>3.217</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2767</v>
+        <v>-2.1184</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8283</v>
+        <v>-2.1387</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5516</v>
+        <v>0.0203</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1931</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6509</v>
+        <v>0.8756</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.607</v>
+        <v>0.9304</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0438</v>
+        <v>-0.0548</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5712</v>
+        <v>-0.3709</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7989</v>
+        <v>0.8568</v>
       </c>
       <c r="X17" t="n">
         <v>-1.2277</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0675</v>
+        <v>0.4812</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0046</v>
+        <v>1.4183</v>
       </c>
       <c r="F18" t="n">
         <v>-0.9372</v>
@@ -1858,10 +1858,10 @@
         <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4689</v>
+        <v>-0.0552</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3311</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U18" t="n">
         <v>-0.1378</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5938</v>
+        <v>-1.2433</v>
       </c>
       <c r="E19" t="n">
-        <v>0.778</v>
+        <v>0.0541</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3718</v>
+        <v>-1.2973</v>
       </c>
       <c r="G19" t="n">
         <v>0.0576</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3253</v>
+        <v>-0.3241</v>
       </c>
       <c r="T19" t="n">
-        <v>0.772</v>
+        <v>0.048</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4466</v>
+        <v>-0.3721</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5559</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5871</v>
+        <v>-1.6589</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.4417</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5116</v>
+        <v>-2.1006</v>
       </c>
       <c r="G20" t="n">
         <v>0.6793</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.004</v>
+        <v>-0.0759</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4691</v>
+        <v>0.048</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5349</v>
+        <v>-0.1239</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4554</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.1329</v>
+        <v>-5.078</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3662</v>
+        <v>-3.4354</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7667</v>
+        <v>-1.6426</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4878</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7723</v>
+        <v>0.2827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5795</v>
+        <v>0.3513</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1928</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3282</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>10.598</v>
+        <v>11.2875</v>
       </c>
       <c r="E22" t="n">
         <v>21.0698</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.4718</v>
+        <v>-9.782499999999999</v>
       </c>
       <c r="G22" t="n">
         <v>12.7581</v>
@@ -2167,16 +2167,16 @@
         <v>-14.481</v>
       </c>
       <c r="R22" t="n">
-        <v>9.6538</v>
+        <v>9.653799999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>4.964500000000001</v>
+        <v>5.654000000000001</v>
       </c>
       <c r="T22" t="n">
         <v>4.2721</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6924999999999999</v>
+        <v>1.382</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2977</v>
